--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -41013,6 +41013,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1768">
+      <c r="A1768" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1768" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1768" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="D1768" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="G1768" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1769" t="n">
+        <v>6050</v>
+      </c>
+      <c r="C1769" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D1769" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1769" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G1769" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -41059,6 +41059,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1770">
+      <c r="A1770" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1770" t="n">
+        <v>8250</v>
+      </c>
+      <c r="C1770" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1770" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G1770" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -41082,6 +41082,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1771">
+      <c r="A1771" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1771" t="n">
+        <v>9900</v>
+      </c>
+      <c r="C1771" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1771" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G1771" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -40923,22 +40923,22 @@
     </row>
     <row r="1764">
       <c r="A1764" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1764" t="n">
-        <v>4400</v>
+        <v>4950</v>
       </c>
       <c r="C1764" t="n">
-        <v>1.00999999046326</v>
+        <v>0.995000004768372</v>
       </c>
       <c r="D1764" t="n">
         <v>0.990000009536743</v>
       </c>
       <c r="E1764" t="n">
-        <v>1</v>
+        <v>0.995000004768372</v>
       </c>
       <c r="F1764" t="n">
-        <v>1.00999999046326</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="G1764" t="s">
         <v>7</v>
@@ -40946,19 +40946,19 @@
     </row>
     <row r="1765">
       <c r="A1765" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1765" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="C1765" t="n">
         <v>1.00999999046326</v>
       </c>
       <c r="D1765" t="n">
-        <v>1.00999999046326</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="E1765" t="n">
-        <v>1.00999999046326</v>
+        <v>1</v>
       </c>
       <c r="F1765" t="n">
         <v>1.00999999046326</v>
@@ -40969,7 +40969,7 @@
     </row>
     <row r="1766">
       <c r="A1766" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1766" t="n">
         <v>0</v>
@@ -40992,22 +40992,22 @@
     </row>
     <row r="1767">
       <c r="A1767" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1767" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="C1767" t="n">
-        <v>0.985000014305115</v>
+        <v>1.00999999046326</v>
       </c>
       <c r="D1767" t="n">
-        <v>0.985000014305115</v>
+        <v>1.00999999046326</v>
       </c>
       <c r="E1767" t="n">
-        <v>0.985000014305115</v>
+        <v>1.00999999046326</v>
       </c>
       <c r="F1767" t="n">
-        <v>0.985000014305115</v>
+        <v>1.00999999046326</v>
       </c>
       <c r="G1767" t="s">
         <v>7</v>
@@ -41015,10 +41015,10 @@
     </row>
     <row r="1768">
       <c r="A1768" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1768" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="C1768" t="n">
         <v>0.985000014305115</v>
@@ -41038,22 +41038,22 @@
     </row>
     <row r="1769">
       <c r="A1769" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1769" t="n">
-        <v>6050</v>
+        <v>0</v>
       </c>
       <c r="C1769" t="n">
-        <v>1.01999998092651</v>
+        <v>0.985000014305115</v>
       </c>
       <c r="D1769" t="n">
-        <v>1</v>
+        <v>0.985000014305115</v>
       </c>
       <c r="E1769" t="n">
-        <v>1</v>
+        <v>0.985000014305115</v>
       </c>
       <c r="F1769" t="n">
-        <v>1.01999998092651</v>
+        <v>0.985000014305115</v>
       </c>
       <c r="G1769" t="s">
         <v>7</v>
@@ -41061,22 +41061,22 @@
     </row>
     <row r="1770">
       <c r="A1770" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1770" t="n">
-        <v>8250</v>
+        <v>6050</v>
       </c>
       <c r="C1770" t="n">
-        <v>1.02999997138977</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="D1770" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1770" t="n">
         <v>1.01999998092651</v>
-      </c>
-      <c r="E1770" t="n">
-        <v>1.01999998092651</v>
-      </c>
-      <c r="F1770" t="n">
-        <v>1.02999997138977</v>
       </c>
       <c r="G1770" t="s">
         <v>7</v>
@@ -41084,24 +41084,47 @@
     </row>
     <row r="1771">
       <c r="A1771" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1771" t="n">
-        <v>9900</v>
+        <v>8250</v>
       </c>
       <c r="C1771" t="n">
-        <v>1.04999995231628</v>
+        <v>1.02999997138977</v>
       </c>
       <c r="D1771" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F1771" t="n">
         <v>1.02999997138977</v>
       </c>
-      <c r="E1771" t="n">
-        <v>1.02999997138977</v>
-      </c>
-      <c r="F1771" t="n">
-        <v>1.03999996185303</v>
-      </c>
       <c r="G1771" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1772" t="n">
+        <v>94600</v>
+      </c>
+      <c r="C1772" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D1772" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="G1772" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100487709045</v>
+        <v>2.06100511550903</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081685066223</v>
+        <v>2.22081661224365</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276248931885</v>
+        <v>2.07276272773743</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663491249084</v>
+        <v>2.04663515090942</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858090877533</v>
+        <v>1.89858102798462</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.8550351858139</v>
+        <v>1.85503506660461</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.7940719127655</v>
+        <v>1.79407203197479</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696268558502</v>
+        <v>1.97696256637573</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896286010742</v>
+        <v>1.01896297931671</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744612216949</v>
+        <v>0.905744671821594</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990787506104</v>
+        <v>1.34990775585175</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783952713013</v>
+        <v>1.41783964633942</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474452495575</v>
+        <v>1.38474440574646</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501034736633</v>
+        <v>1.27501046657562</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378125190735</v>
+        <v>1.32378137111664</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409029006958</v>
+        <v>1.52409040927887</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441699028015</v>
+        <v>1.45441687107086</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113697052002</v>
+        <v>1.30113708972931</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042114257812</v>
+        <v>1.40042126178741</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054456710815</v>
+        <v>1.48054444789886</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706115245819</v>
+        <v>1.47706127166748</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -46496,6 +46496,32 @@
         <v>1.14999997615814</v>
       </c>
       <c r="H1774" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1775" t="n">
+        <v>11550</v>
+      </c>
+      <c r="C1775" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="D1775" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="E1775" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F1775" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="G1775" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="H1775" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100511550903</v>
+        <v>2.06100487709045</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081661224365</v>
+        <v>2.22081685066223</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534410476685</v>
+        <v>2.05534434318542</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276272773743</v>
+        <v>2.07276248931885</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663515090942</v>
+        <v>2.04663491249084</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729010105133</v>
+        <v>1.90729022026062</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858102798462</v>
+        <v>1.89858090877533</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954430103302</v>
+        <v>1.95954442024231</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954430103302</v>
+        <v>1.95954442024231</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.85503506660461</v>
+        <v>1.8550351858139</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.79407203197479</v>
+        <v>1.7940719127655</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696256637573</v>
+        <v>1.97696268558502</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534410476685</v>
+        <v>2.05534434318542</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729010105133</v>
+        <v>1.90729022026062</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896297931671</v>
+        <v>1.01896286010742</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744671821594</v>
+        <v>0.905744612216949</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927201747894</v>
+        <v>1.21927213668823</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927201747894</v>
+        <v>1.21927213668823</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894460201263</v>
+        <v>1.28894448280334</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894460201263</v>
+        <v>1.28894448280334</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990775585175</v>
+        <v>1.34990787506104</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783964633942</v>
+        <v>1.41783952713013</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474440574646</v>
+        <v>1.38474452495575</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501046657562</v>
+        <v>1.27501034736633</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378137111664</v>
+        <v>1.32378125190735</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409040927887</v>
+        <v>1.52409029006958</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441687107086</v>
+        <v>1.45441699028015</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113708972931</v>
+        <v>1.30113697052002</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042126178741</v>
+        <v>1.40042114257812</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054444789886</v>
+        <v>1.48054456710815</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706127166748</v>
+        <v>1.47706115245819</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -46522,6 +46522,32 @@
         <v>1.12000000476837</v>
       </c>
       <c r="H1775" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1776" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C1776" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D1776" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G1776" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="H1776" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100487709045</v>
+        <v>2.06100511550903</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081685066223</v>
+        <v>2.22081661224365</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276248931885</v>
+        <v>2.07276272773743</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663491249084</v>
+        <v>2.04663515090942</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858090877533</v>
+        <v>1.89858102798462</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.8550351858139</v>
+        <v>1.85503506660461</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.7940719127655</v>
+        <v>1.79407203197479</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696268558502</v>
+        <v>1.97696256637573</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896286010742</v>
+        <v>1.01896297931671</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744612216949</v>
+        <v>0.905744671821594</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990787506104</v>
+        <v>1.34990775585175</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783952713013</v>
+        <v>1.41783964633942</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474452495575</v>
+        <v>1.38474440574646</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501034736633</v>
+        <v>1.27501046657562</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378125190735</v>
+        <v>1.32378137111664</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409029006958</v>
+        <v>1.52409040927887</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441699028015</v>
+        <v>1.45441687107086</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113697052002</v>
+        <v>1.30113708972931</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042114257812</v>
+        <v>1.40042126178741</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054456710815</v>
+        <v>1.48054444789886</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706115245819</v>
+        <v>1.47706127166748</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -46548,6 +46548,32 @@
         <v>1.13999998569489</v>
       </c>
       <c r="H1776" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1777" t="n">
+        <v>12650</v>
+      </c>
+      <c r="C1777" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D1777" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="E1777" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="F1777" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="G1777" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="H1777" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -46559,7 +46559,7 @@
         <v>12650</v>
       </c>
       <c r="C1777" t="n">
-        <v>1.1599999666214</v>
+        <v>1.19000005722046</v>
       </c>
       <c r="D1777" t="n">
         <v>1.12000000476837</v>
@@ -46574,6 +46574,32 @@
         <v>1.19000005722046</v>
       </c>
       <c r="H1777" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1778" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C1778" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D1778" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="E1778" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F1778" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="G1778" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="H1778" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -46655,6 +46655,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1781">
+      <c r="A1781" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1781" t="n">
+        <v>37400</v>
+      </c>
+      <c r="C1781" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D1781" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E1781" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F1781" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G1781" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="H1781" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -41397,8 +41397,31 @@
       <c r="E1784" t="n">
         <v>1.12000000476837</v>
       </c>
-      <c r="F1784"/>
+      <c r="F1784" t="n">
+        <v>1.17999994754791</v>
+      </c>
       <c r="G1784" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1785" t="n">
+        <v>6600</v>
+      </c>
+      <c r="C1785" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D1785" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E1785" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F1785"/>
+      <c r="G1785" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -41420,8 +41420,31 @@
       <c r="E1785" t="n">
         <v>1.1599999666214</v>
       </c>
-      <c r="F1785"/>
+      <c r="F1785" t="n">
+        <v>1.17999994754791</v>
+      </c>
       <c r="G1785" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1786" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C1786" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D1786" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E1786" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F1786"/>
+      <c r="G1786" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -41443,7 +41443,9 @@
       <c r="E1786" t="n">
         <v>1.1599999666214</v>
       </c>
-      <c r="F1786"/>
+      <c r="F1786" t="n">
+        <v>1.1599999666214</v>
+      </c>
       <c r="G1786" t="s">
         <v>7</v>
       </c>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -41450,6 +41450,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1787">
+      <c r="A1787" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1787" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1787" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D1787" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E1787" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F1787" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G1787" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1788" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C1788" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D1788" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E1788" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="F1788"/>
+      <c r="G1788" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -41496,6 +41496,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1789">
+      <c r="A1789" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1789" t="n">
+        <v>10450</v>
+      </c>
+      <c r="C1789" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D1789" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="E1789" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="F1789" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G1789" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -46941,6 +46941,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1792">
+      <c r="A1792" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1792" t="n">
+        <v>39050</v>
+      </c>
+      <c r="C1792" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="D1792" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E1792" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="F1792" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="G1792" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="H1792" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100487709045</v>
+        <v>2.06100511550903</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081685066223</v>
+        <v>2.22081661224365</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276248931885</v>
+        <v>2.07276272773743</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663491249084</v>
+        <v>2.04663515090942</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858090877533</v>
+        <v>1.89858102798462</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.8550351858139</v>
+        <v>1.85503506660461</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.7940719127655</v>
+        <v>1.79407203197479</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696268558502</v>
+        <v>1.97696256637573</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896286010742</v>
+        <v>1.01896297931671</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744612216949</v>
+        <v>0.905744671821594</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990787506104</v>
+        <v>1.34990775585175</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783952713013</v>
+        <v>1.41783964633942</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474452495575</v>
+        <v>1.38474440574646</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501034736633</v>
+        <v>1.27501046657562</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378125190735</v>
+        <v>1.32378137111664</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409029006958</v>
+        <v>1.52409040927887</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441699028015</v>
+        <v>1.45441687107086</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113697052002</v>
+        <v>1.30113708972931</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042114257812</v>
+        <v>1.40042126178741</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054456710815</v>
+        <v>1.48054444789886</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706115245819</v>
+        <v>1.47706127166748</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -46964,6 +46964,32 @@
         <v>1.25999999046326</v>
       </c>
       <c r="H1792" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1793" t="n">
+        <v>12100</v>
+      </c>
+      <c r="C1793" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D1793" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E1793" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="F1793" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="G1793" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="H1793" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -52375,6 +52375,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1794">
+      <c r="A1794" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1794" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1794" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D1794" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E1794" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F1794" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G1794" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H1794" t="n">
+        <v>21450</v>
+      </c>
+      <c r="I1794" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1795" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1795" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="D1795" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="E1795" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F1795" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="G1795" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="H1795" t="n">
+        <v>15400</v>
+      </c>
+      <c r="I1795" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -52433,6 +52433,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1796">
+      <c r="A1796" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1796" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1796" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D1796" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="E1796" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F1796" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G1796" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H1796" t="n">
+        <v>4400</v>
+      </c>
+      <c r="I1796" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -52462,6 +52462,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1797">
+      <c r="A1797" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1797" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1797" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D1797" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E1797" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F1797" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G1797" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H1797" t="n">
+        <v>550</v>
+      </c>
+      <c r="I1797" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H2" t="n">
         <v>789800</v>
@@ -514,7 +514,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100511550903</v>
+        <v>2.06100487709045</v>
       </c>
       <c r="H5" t="n">
         <v>390500</v>
@@ -543,7 +543,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H6" t="n">
         <v>204600</v>
@@ -572,7 +572,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H7" t="n">
         <v>304700</v>
@@ -601,7 +601,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H8" t="n">
         <v>64900</v>
@@ -630,7 +630,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H9" t="n">
         <v>221100</v>
@@ -688,7 +688,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H11" t="n">
         <v>48400</v>
@@ -717,7 +717,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H12" t="n">
         <v>114400</v>
@@ -833,7 +833,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081661224365</v>
+        <v>2.22081685066223</v>
       </c>
       <c r="H16" t="n">
         <v>167200</v>
@@ -1152,7 +1152,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534410476685</v>
+        <v>2.05534434318542</v>
       </c>
       <c r="H27" t="n">
         <v>31900</v>
@@ -1181,7 +1181,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H28" t="n">
         <v>36300</v>
@@ -1268,7 +1268,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H31" t="n">
         <v>28600</v>
@@ -1384,7 +1384,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H35" t="n">
         <v>13200</v>
@@ -1529,7 +1529,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276272773743</v>
+        <v>2.07276248931885</v>
       </c>
       <c r="H40" t="n">
         <v>35200</v>
@@ -1558,7 +1558,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663515090942</v>
+        <v>2.04663491249084</v>
       </c>
       <c r="H41" t="n">
         <v>5500</v>
@@ -1587,7 +1587,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H42" t="n">
         <v>14300</v>
@@ -1616,7 +1616,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H43" t="n">
         <v>44000</v>
@@ -1645,7 +1645,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H44" t="n">
         <v>13200</v>
@@ -1674,7 +1674,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H45" t="n">
         <v>22000</v>
@@ -1703,7 +1703,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H46" t="n">
         <v>9900</v>
@@ -1732,7 +1732,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H47" t="n">
         <v>202400</v>
@@ -1761,7 +1761,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H48" t="n">
         <v>19800</v>
@@ -1848,7 +1848,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H51" t="n">
         <v>24200</v>
@@ -1877,7 +1877,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H52" t="n">
         <v>77000</v>
@@ -1935,7 +1935,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729010105133</v>
+        <v>1.90729022026062</v>
       </c>
       <c r="H54" t="n">
         <v>37400</v>
@@ -1993,7 +1993,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858102798462</v>
+        <v>1.89858090877533</v>
       </c>
       <c r="H56" t="n">
         <v>31900</v>
@@ -2022,7 +2022,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H57" t="n">
         <v>2200</v>
@@ -2080,7 +2080,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H59" t="n">
         <v>48400</v>
@@ -2167,7 +2167,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954430103302</v>
+        <v>1.95954442024231</v>
       </c>
       <c r="H62" t="n">
         <v>18700</v>
@@ -2254,7 +2254,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954430103302</v>
+        <v>1.95954442024231</v>
       </c>
       <c r="H65" t="n">
         <v>20900</v>
@@ -2486,7 +2486,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H73" t="n">
         <v>14300</v>
@@ -2544,7 +2544,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H75" t="n">
         <v>8800</v>
@@ -2573,7 +2573,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.85503506660461</v>
+        <v>1.8550351858139</v>
       </c>
       <c r="H76" t="n">
         <v>6600</v>
@@ -2602,7 +2602,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H77" t="n">
         <v>4400</v>
@@ -2718,7 +2718,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H81" t="n">
         <v>5500</v>
@@ -2805,7 +2805,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.79407203197479</v>
+        <v>1.7940719127655</v>
       </c>
       <c r="H84" t="n">
         <v>7700</v>
@@ -2950,7 +2950,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H89" t="n">
         <v>77000</v>
@@ -3037,7 +3037,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H92" t="n">
         <v>78100</v>
@@ -3066,7 +3066,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696256637573</v>
+        <v>1.97696268558502</v>
       </c>
       <c r="H93" t="n">
         <v>28600</v>
@@ -3095,7 +3095,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H94" t="n">
         <v>63800</v>
@@ -3124,7 +3124,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534410476685</v>
+        <v>2.05534434318542</v>
       </c>
       <c r="H95" t="n">
         <v>22000</v>
@@ -3182,7 +3182,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H97" t="n">
         <v>79200</v>
@@ -3211,7 +3211,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H98" t="n">
         <v>44000</v>
@@ -3240,7 +3240,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729010105133</v>
+        <v>1.90729022026062</v>
       </c>
       <c r="H99" t="n">
         <v>19800</v>
@@ -3298,7 +3298,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H101" t="n">
         <v>9900</v>
@@ -3617,7 +3617,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896297931671</v>
+        <v>1.01896286010742</v>
       </c>
       <c r="H112" t="n">
         <v>29700</v>
@@ -3762,7 +3762,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744671821594</v>
+        <v>0.905744612216949</v>
       </c>
       <c r="H117" t="n">
         <v>7700</v>
@@ -3878,7 +3878,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927201747894</v>
+        <v>1.21927213668823</v>
       </c>
       <c r="H121" t="n">
         <v>14300</v>
@@ -3907,7 +3907,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927201747894</v>
+        <v>1.21927213668823</v>
       </c>
       <c r="H122" t="n">
         <v>45100</v>
@@ -3936,7 +3936,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894460201263</v>
+        <v>1.28894448280334</v>
       </c>
       <c r="H123" t="n">
         <v>45100</v>
@@ -3965,7 +3965,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894460201263</v>
+        <v>1.28894448280334</v>
       </c>
       <c r="H124" t="n">
         <v>34100</v>
@@ -4139,7 +4139,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990775585175</v>
+        <v>1.34990787506104</v>
       </c>
       <c r="H130" t="n">
         <v>6600</v>
@@ -4168,7 +4168,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H131" t="n">
         <v>15400</v>
@@ -4197,7 +4197,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H132" t="n">
         <v>60500</v>
@@ -4226,7 +4226,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783964633942</v>
+        <v>1.41783952713013</v>
       </c>
       <c r="H133" t="n">
         <v>38500</v>
@@ -4284,7 +4284,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474440574646</v>
+        <v>1.38474452495575</v>
       </c>
       <c r="H135" t="n">
         <v>6600</v>
@@ -4342,7 +4342,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501046657562</v>
+        <v>1.27501034736633</v>
       </c>
       <c r="H137" t="n">
         <v>9900</v>
@@ -4400,7 +4400,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378137111664</v>
+        <v>1.32378125190735</v>
       </c>
       <c r="H139" t="n">
         <v>17600</v>
@@ -4429,7 +4429,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409040927887</v>
+        <v>1.52409029006958</v>
       </c>
       <c r="H140" t="n">
         <v>67100</v>
@@ -4487,7 +4487,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441687107086</v>
+        <v>1.45441699028015</v>
       </c>
       <c r="H142" t="n">
         <v>73700</v>
@@ -4574,7 +4574,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113708972931</v>
+        <v>1.30113697052002</v>
       </c>
       <c r="H145" t="n">
         <v>9900</v>
@@ -4632,7 +4632,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H147" t="n">
         <v>14300</v>
@@ -4748,7 +4748,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H151" t="n">
         <v>8800</v>
@@ -4777,7 +4777,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042126178741</v>
+        <v>1.40042114257812</v>
       </c>
       <c r="H152" t="n">
         <v>7700</v>
@@ -4806,7 +4806,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H153" t="n">
         <v>3300</v>
@@ -4835,7 +4835,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054444789886</v>
+        <v>1.48054456710815</v>
       </c>
       <c r="H163" t="n">
         <v>9900</v>
@@ -5154,7 +5154,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706127166748</v>
+        <v>1.47706115245819</v>
       </c>
       <c r="H165" t="n">
         <v>4400</v>
@@ -52488,6 +52488,35 @@
         <v>550</v>
       </c>
       <c r="I1797" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1798" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1798" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D1798" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E1798" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F1798" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G1798" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="H1798" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I1798" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H2" t="n">
         <v>789800</v>
@@ -514,7 +514,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100487709045</v>
+        <v>2.06100511550903</v>
       </c>
       <c r="H5" t="n">
         <v>390500</v>
@@ -543,7 +543,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H6" t="n">
         <v>204600</v>
@@ -572,7 +572,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H7" t="n">
         <v>304700</v>
@@ -601,7 +601,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H8" t="n">
         <v>64900</v>
@@ -630,7 +630,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H9" t="n">
         <v>221100</v>
@@ -688,7 +688,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H11" t="n">
         <v>48400</v>
@@ -717,7 +717,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H12" t="n">
         <v>114400</v>
@@ -833,7 +833,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081685066223</v>
+        <v>2.22081661224365</v>
       </c>
       <c r="H16" t="n">
         <v>167200</v>
@@ -1152,7 +1152,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H27" t="n">
         <v>31900</v>
@@ -1181,7 +1181,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H28" t="n">
         <v>36300</v>
@@ -1268,7 +1268,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H31" t="n">
         <v>28600</v>
@@ -1384,7 +1384,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H35" t="n">
         <v>13200</v>
@@ -1529,7 +1529,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276248931885</v>
+        <v>2.07276272773743</v>
       </c>
       <c r="H40" t="n">
         <v>35200</v>
@@ -1558,7 +1558,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663491249084</v>
+        <v>2.04663515090942</v>
       </c>
       <c r="H41" t="n">
         <v>5500</v>
@@ -1587,7 +1587,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H42" t="n">
         <v>14300</v>
@@ -1616,7 +1616,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H43" t="n">
         <v>44000</v>
@@ -1645,7 +1645,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H44" t="n">
         <v>13200</v>
@@ -1674,7 +1674,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H45" t="n">
         <v>22000</v>
@@ -1703,7 +1703,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H46" t="n">
         <v>9900</v>
@@ -1732,7 +1732,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H47" t="n">
         <v>202400</v>
@@ -1761,7 +1761,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H48" t="n">
         <v>19800</v>
@@ -1848,7 +1848,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H51" t="n">
         <v>24200</v>
@@ -1877,7 +1877,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H52" t="n">
         <v>77000</v>
@@ -1935,7 +1935,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H54" t="n">
         <v>37400</v>
@@ -1993,7 +1993,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858090877533</v>
+        <v>1.89858102798462</v>
       </c>
       <c r="H56" t="n">
         <v>31900</v>
@@ -2022,7 +2022,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H57" t="n">
         <v>2200</v>
@@ -2080,7 +2080,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H59" t="n">
         <v>48400</v>
@@ -2167,7 +2167,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H62" t="n">
         <v>18700</v>
@@ -2254,7 +2254,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H65" t="n">
         <v>20900</v>
@@ -2486,7 +2486,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H73" t="n">
         <v>14300</v>
@@ -2544,7 +2544,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H75" t="n">
         <v>8800</v>
@@ -2573,7 +2573,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.8550351858139</v>
+        <v>1.85503506660461</v>
       </c>
       <c r="H76" t="n">
         <v>6600</v>
@@ -2602,7 +2602,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H77" t="n">
         <v>4400</v>
@@ -2718,7 +2718,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H81" t="n">
         <v>5500</v>
@@ -2805,7 +2805,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.7940719127655</v>
+        <v>1.79407203197479</v>
       </c>
       <c r="H84" t="n">
         <v>7700</v>
@@ -2950,7 +2950,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H89" t="n">
         <v>77000</v>
@@ -3037,7 +3037,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H92" t="n">
         <v>78100</v>
@@ -3066,7 +3066,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696268558502</v>
+        <v>1.97696256637573</v>
       </c>
       <c r="H93" t="n">
         <v>28600</v>
@@ -3095,7 +3095,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H94" t="n">
         <v>63800</v>
@@ -3124,7 +3124,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H95" t="n">
         <v>22000</v>
@@ -3182,7 +3182,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H97" t="n">
         <v>79200</v>
@@ -3211,7 +3211,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H98" t="n">
         <v>44000</v>
@@ -3240,7 +3240,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H99" t="n">
         <v>19800</v>
@@ -3298,7 +3298,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H101" t="n">
         <v>9900</v>
@@ -3617,7 +3617,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896286010742</v>
+        <v>1.01896297931671</v>
       </c>
       <c r="H112" t="n">
         <v>29700</v>
@@ -3762,7 +3762,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744612216949</v>
+        <v>0.905744671821594</v>
       </c>
       <c r="H117" t="n">
         <v>7700</v>
@@ -3878,7 +3878,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H121" t="n">
         <v>14300</v>
@@ -3907,7 +3907,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H122" t="n">
         <v>45100</v>
@@ -3936,7 +3936,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H123" t="n">
         <v>45100</v>
@@ -3965,7 +3965,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H124" t="n">
         <v>34100</v>
@@ -4139,7 +4139,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990787506104</v>
+        <v>1.34990775585175</v>
       </c>
       <c r="H130" t="n">
         <v>6600</v>
@@ -4168,7 +4168,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H131" t="n">
         <v>15400</v>
@@ -4197,7 +4197,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H132" t="n">
         <v>60500</v>
@@ -4226,7 +4226,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783952713013</v>
+        <v>1.41783964633942</v>
       </c>
       <c r="H133" t="n">
         <v>38500</v>
@@ -4284,7 +4284,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474452495575</v>
+        <v>1.38474440574646</v>
       </c>
       <c r="H135" t="n">
         <v>6600</v>
@@ -4342,7 +4342,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501034736633</v>
+        <v>1.27501046657562</v>
       </c>
       <c r="H137" t="n">
         <v>9900</v>
@@ -4400,7 +4400,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378125190735</v>
+        <v>1.32378137111664</v>
       </c>
       <c r="H139" t="n">
         <v>17600</v>
@@ -4429,7 +4429,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409029006958</v>
+        <v>1.52409040927887</v>
       </c>
       <c r="H140" t="n">
         <v>67100</v>
@@ -4487,7 +4487,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441699028015</v>
+        <v>1.45441687107086</v>
       </c>
       <c r="H142" t="n">
         <v>73700</v>
@@ -4574,7 +4574,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113697052002</v>
+        <v>1.30113708972931</v>
       </c>
       <c r="H145" t="n">
         <v>9900</v>
@@ -4632,7 +4632,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H147" t="n">
         <v>14300</v>
@@ -4748,7 +4748,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H151" t="n">
         <v>8800</v>
@@ -4777,7 +4777,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042114257812</v>
+        <v>1.40042126178741</v>
       </c>
       <c r="H152" t="n">
         <v>7700</v>
@@ -4806,7 +4806,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H153" t="n">
         <v>3300</v>
@@ -4835,7 +4835,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054456710815</v>
+        <v>1.48054444789886</v>
       </c>
       <c r="H163" t="n">
         <v>9900</v>
@@ -5154,7 +5154,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706115245819</v>
+        <v>1.47706127166748</v>
       </c>
       <c r="H165" t="n">
         <v>4400</v>
@@ -52505,7 +52505,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.17999994754791</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="F1798" t="n">
         <v>1.16999995708466</v>
@@ -52517,6 +52517,35 @@
         <v>9900</v>
       </c>
       <c r="I1798" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1799" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1799" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D1799" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="E1799" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F1799" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="G1799" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="H1799" t="n">
+        <v>3850</v>
+      </c>
+      <c r="I1799" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H2" t="n">
         <v>789800</v>
@@ -514,7 +514,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100511550903</v>
+        <v>2.06100487709045</v>
       </c>
       <c r="H5" t="n">
         <v>390500</v>
@@ -543,7 +543,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H6" t="n">
         <v>204600</v>
@@ -572,7 +572,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H7" t="n">
         <v>304700</v>
@@ -601,7 +601,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H8" t="n">
         <v>64900</v>
@@ -630,7 +630,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H9" t="n">
         <v>221100</v>
@@ -688,7 +688,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H11" t="n">
         <v>48400</v>
@@ -717,7 +717,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H12" t="n">
         <v>114400</v>
@@ -833,7 +833,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081661224365</v>
+        <v>2.22081685066223</v>
       </c>
       <c r="H16" t="n">
         <v>167200</v>
@@ -1152,7 +1152,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534410476685</v>
+        <v>2.05534434318542</v>
       </c>
       <c r="H27" t="n">
         <v>31900</v>
@@ -1181,7 +1181,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H28" t="n">
         <v>36300</v>
@@ -1268,7 +1268,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H31" t="n">
         <v>28600</v>
@@ -1384,7 +1384,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H35" t="n">
         <v>13200</v>
@@ -1529,7 +1529,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276272773743</v>
+        <v>2.07276248931885</v>
       </c>
       <c r="H40" t="n">
         <v>35200</v>
@@ -1558,7 +1558,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663515090942</v>
+        <v>2.04663491249084</v>
       </c>
       <c r="H41" t="n">
         <v>5500</v>
@@ -1587,7 +1587,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H42" t="n">
         <v>14300</v>
@@ -1616,7 +1616,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H43" t="n">
         <v>44000</v>
@@ -1645,7 +1645,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H44" t="n">
         <v>13200</v>
@@ -1674,7 +1674,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H45" t="n">
         <v>22000</v>
@@ -1703,7 +1703,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H46" t="n">
         <v>9900</v>
@@ -1732,7 +1732,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H47" t="n">
         <v>202400</v>
@@ -1761,7 +1761,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H48" t="n">
         <v>19800</v>
@@ -1848,7 +1848,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H51" t="n">
         <v>24200</v>
@@ -1877,7 +1877,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H52" t="n">
         <v>77000</v>
@@ -1935,7 +1935,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729010105133</v>
+        <v>1.90729022026062</v>
       </c>
       <c r="H54" t="n">
         <v>37400</v>
@@ -1993,7 +1993,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858102798462</v>
+        <v>1.89858090877533</v>
       </c>
       <c r="H56" t="n">
         <v>31900</v>
@@ -2022,7 +2022,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H57" t="n">
         <v>2200</v>
@@ -2080,7 +2080,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H59" t="n">
         <v>48400</v>
@@ -2167,7 +2167,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954430103302</v>
+        <v>1.95954442024231</v>
       </c>
       <c r="H62" t="n">
         <v>18700</v>
@@ -2254,7 +2254,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954430103302</v>
+        <v>1.95954442024231</v>
       </c>
       <c r="H65" t="n">
         <v>20900</v>
@@ -2486,7 +2486,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H73" t="n">
         <v>14300</v>
@@ -2544,7 +2544,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H75" t="n">
         <v>8800</v>
@@ -2573,7 +2573,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.85503506660461</v>
+        <v>1.8550351858139</v>
       </c>
       <c r="H76" t="n">
         <v>6600</v>
@@ -2602,7 +2602,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H77" t="n">
         <v>4400</v>
@@ -2718,7 +2718,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H81" t="n">
         <v>5500</v>
@@ -2805,7 +2805,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.79407203197479</v>
+        <v>1.7940719127655</v>
       </c>
       <c r="H84" t="n">
         <v>7700</v>
@@ -2950,7 +2950,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H89" t="n">
         <v>77000</v>
@@ -3037,7 +3037,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H92" t="n">
         <v>78100</v>
@@ -3066,7 +3066,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696256637573</v>
+        <v>1.97696268558502</v>
       </c>
       <c r="H93" t="n">
         <v>28600</v>
@@ -3095,7 +3095,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H94" t="n">
         <v>63800</v>
@@ -3124,7 +3124,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534410476685</v>
+        <v>2.05534434318542</v>
       </c>
       <c r="H95" t="n">
         <v>22000</v>
@@ -3182,7 +3182,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H97" t="n">
         <v>79200</v>
@@ -3211,7 +3211,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H98" t="n">
         <v>44000</v>
@@ -3240,7 +3240,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729010105133</v>
+        <v>1.90729022026062</v>
       </c>
       <c r="H99" t="n">
         <v>19800</v>
@@ -3298,7 +3298,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H101" t="n">
         <v>9900</v>
@@ -3617,7 +3617,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896297931671</v>
+        <v>1.01896286010742</v>
       </c>
       <c r="H112" t="n">
         <v>29700</v>
@@ -3762,7 +3762,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744671821594</v>
+        <v>0.905744612216949</v>
       </c>
       <c r="H117" t="n">
         <v>7700</v>
@@ -3878,7 +3878,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927201747894</v>
+        <v>1.21927213668823</v>
       </c>
       <c r="H121" t="n">
         <v>14300</v>
@@ -3907,7 +3907,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927201747894</v>
+        <v>1.21927213668823</v>
       </c>
       <c r="H122" t="n">
         <v>45100</v>
@@ -3936,7 +3936,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894460201263</v>
+        <v>1.28894448280334</v>
       </c>
       <c r="H123" t="n">
         <v>45100</v>
@@ -3965,7 +3965,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894460201263</v>
+        <v>1.28894448280334</v>
       </c>
       <c r="H124" t="n">
         <v>34100</v>
@@ -4139,7 +4139,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990775585175</v>
+        <v>1.34990787506104</v>
       </c>
       <c r="H130" t="n">
         <v>6600</v>
@@ -4168,7 +4168,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H131" t="n">
         <v>15400</v>
@@ -4197,7 +4197,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H132" t="n">
         <v>60500</v>
@@ -4226,7 +4226,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783964633942</v>
+        <v>1.41783952713013</v>
       </c>
       <c r="H133" t="n">
         <v>38500</v>
@@ -4284,7 +4284,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474440574646</v>
+        <v>1.38474452495575</v>
       </c>
       <c r="H135" t="n">
         <v>6600</v>
@@ -4342,7 +4342,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501046657562</v>
+        <v>1.27501034736633</v>
       </c>
       <c r="H137" t="n">
         <v>9900</v>
@@ -4400,7 +4400,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378137111664</v>
+        <v>1.32378125190735</v>
       </c>
       <c r="H139" t="n">
         <v>17600</v>
@@ -4429,7 +4429,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409040927887</v>
+        <v>1.52409029006958</v>
       </c>
       <c r="H140" t="n">
         <v>67100</v>
@@ -4487,7 +4487,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441687107086</v>
+        <v>1.45441699028015</v>
       </c>
       <c r="H142" t="n">
         <v>73700</v>
@@ -4574,7 +4574,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113708972931</v>
+        <v>1.30113697052002</v>
       </c>
       <c r="H145" t="n">
         <v>9900</v>
@@ -4632,7 +4632,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H147" t="n">
         <v>14300</v>
@@ -4748,7 +4748,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H151" t="n">
         <v>8800</v>
@@ -4777,7 +4777,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042126178741</v>
+        <v>1.40042114257812</v>
       </c>
       <c r="H152" t="n">
         <v>7700</v>
@@ -4806,7 +4806,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H153" t="n">
         <v>3300</v>
@@ -4835,7 +4835,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054444789886</v>
+        <v>1.48054456710815</v>
       </c>
       <c r="H163" t="n">
         <v>9900</v>
@@ -5154,7 +5154,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706127166748</v>
+        <v>1.47706115245819</v>
       </c>
       <c r="H165" t="n">
         <v>4400</v>
@@ -52543,9 +52543,38 @@
         <v>1.14999997615814</v>
       </c>
       <c r="H1799" t="n">
-        <v>3850</v>
+        <v>4950</v>
       </c>
       <c r="I1799" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1800" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1800" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D1800" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E1800" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F1800" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G1800" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="H1800" t="n">
+        <v>38500</v>
+      </c>
+      <c r="I1800" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H2" t="n">
         <v>789800</v>
@@ -514,7 +514,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100487709045</v>
+        <v>2.06100511550903</v>
       </c>
       <c r="H5" t="n">
         <v>390500</v>
@@ -543,7 +543,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H6" t="n">
         <v>204600</v>
@@ -572,7 +572,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H7" t="n">
         <v>304700</v>
@@ -601,7 +601,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H8" t="n">
         <v>64900</v>
@@ -630,7 +630,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H9" t="n">
         <v>221100</v>
@@ -688,7 +688,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H11" t="n">
         <v>48400</v>
@@ -717,7 +717,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H12" t="n">
         <v>114400</v>
@@ -833,7 +833,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081685066223</v>
+        <v>2.22081661224365</v>
       </c>
       <c r="H16" t="n">
         <v>167200</v>
@@ -1152,7 +1152,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H27" t="n">
         <v>31900</v>
@@ -1181,7 +1181,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H28" t="n">
         <v>36300</v>
@@ -1268,7 +1268,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H31" t="n">
         <v>28600</v>
@@ -1384,7 +1384,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H35" t="n">
         <v>13200</v>
@@ -1529,7 +1529,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276248931885</v>
+        <v>2.07276272773743</v>
       </c>
       <c r="H40" t="n">
         <v>35200</v>
@@ -1558,7 +1558,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663491249084</v>
+        <v>2.04663515090942</v>
       </c>
       <c r="H41" t="n">
         <v>5500</v>
@@ -1587,7 +1587,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H42" t="n">
         <v>14300</v>
@@ -1616,7 +1616,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H43" t="n">
         <v>44000</v>
@@ -1645,7 +1645,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H44" t="n">
         <v>13200</v>
@@ -1674,7 +1674,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H45" t="n">
         <v>22000</v>
@@ -1703,7 +1703,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H46" t="n">
         <v>9900</v>
@@ -1732,7 +1732,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H47" t="n">
         <v>202400</v>
@@ -1761,7 +1761,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H48" t="n">
         <v>19800</v>
@@ -1848,7 +1848,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H51" t="n">
         <v>24200</v>
@@ -1877,7 +1877,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H52" t="n">
         <v>77000</v>
@@ -1935,7 +1935,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H54" t="n">
         <v>37400</v>
@@ -1993,7 +1993,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858090877533</v>
+        <v>1.89858102798462</v>
       </c>
       <c r="H56" t="n">
         <v>31900</v>
@@ -2022,7 +2022,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H57" t="n">
         <v>2200</v>
@@ -2080,7 +2080,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H59" t="n">
         <v>48400</v>
@@ -2167,7 +2167,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H62" t="n">
         <v>18700</v>
@@ -2254,7 +2254,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H65" t="n">
         <v>20900</v>
@@ -2486,7 +2486,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H73" t="n">
         <v>14300</v>
@@ -2544,7 +2544,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H75" t="n">
         <v>8800</v>
@@ -2573,7 +2573,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.8550351858139</v>
+        <v>1.85503506660461</v>
       </c>
       <c r="H76" t="n">
         <v>6600</v>
@@ -2602,7 +2602,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H77" t="n">
         <v>4400</v>
@@ -2718,7 +2718,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H81" t="n">
         <v>5500</v>
@@ -2805,7 +2805,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.7940719127655</v>
+        <v>1.79407203197479</v>
       </c>
       <c r="H84" t="n">
         <v>7700</v>
@@ -2950,7 +2950,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H89" t="n">
         <v>77000</v>
@@ -3037,7 +3037,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H92" t="n">
         <v>78100</v>
@@ -3066,7 +3066,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696268558502</v>
+        <v>1.97696256637573</v>
       </c>
       <c r="H93" t="n">
         <v>28600</v>
@@ -3095,7 +3095,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H94" t="n">
         <v>63800</v>
@@ -3124,7 +3124,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H95" t="n">
         <v>22000</v>
@@ -3182,7 +3182,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H97" t="n">
         <v>79200</v>
@@ -3211,7 +3211,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H98" t="n">
         <v>44000</v>
@@ -3240,7 +3240,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H99" t="n">
         <v>19800</v>
@@ -3298,7 +3298,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H101" t="n">
         <v>9900</v>
@@ -3617,7 +3617,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896286010742</v>
+        <v>1.01896297931671</v>
       </c>
       <c r="H112" t="n">
         <v>29700</v>
@@ -3762,7 +3762,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744612216949</v>
+        <v>0.905744671821594</v>
       </c>
       <c r="H117" t="n">
         <v>7700</v>
@@ -3878,7 +3878,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H121" t="n">
         <v>14300</v>
@@ -3907,7 +3907,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H122" t="n">
         <v>45100</v>
@@ -3936,7 +3936,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H123" t="n">
         <v>45100</v>
@@ -3965,7 +3965,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H124" t="n">
         <v>34100</v>
@@ -4139,7 +4139,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990787506104</v>
+        <v>1.34990775585175</v>
       </c>
       <c r="H130" t="n">
         <v>6600</v>
@@ -4168,7 +4168,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H131" t="n">
         <v>15400</v>
@@ -4197,7 +4197,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H132" t="n">
         <v>60500</v>
@@ -4226,7 +4226,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783952713013</v>
+        <v>1.41783964633942</v>
       </c>
       <c r="H133" t="n">
         <v>38500</v>
@@ -4284,7 +4284,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474452495575</v>
+        <v>1.38474440574646</v>
       </c>
       <c r="H135" t="n">
         <v>6600</v>
@@ -4342,7 +4342,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501034736633</v>
+        <v>1.27501046657562</v>
       </c>
       <c r="H137" t="n">
         <v>9900</v>
@@ -4400,7 +4400,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378125190735</v>
+        <v>1.32378137111664</v>
       </c>
       <c r="H139" t="n">
         <v>17600</v>
@@ -4429,7 +4429,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409029006958</v>
+        <v>1.52409040927887</v>
       </c>
       <c r="H140" t="n">
         <v>67100</v>
@@ -4487,7 +4487,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441699028015</v>
+        <v>1.45441687107086</v>
       </c>
       <c r="H142" t="n">
         <v>73700</v>
@@ -4574,7 +4574,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113697052002</v>
+        <v>1.30113708972931</v>
       </c>
       <c r="H145" t="n">
         <v>9900</v>
@@ -4632,7 +4632,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H147" t="n">
         <v>14300</v>
@@ -4748,7 +4748,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H151" t="n">
         <v>8800</v>
@@ -4777,7 +4777,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042114257812</v>
+        <v>1.40042126178741</v>
       </c>
       <c r="H152" t="n">
         <v>7700</v>
@@ -4806,7 +4806,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H153" t="n">
         <v>3300</v>
@@ -4835,7 +4835,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054456710815</v>
+        <v>1.48054444789886</v>
       </c>
       <c r="H163" t="n">
         <v>9900</v>
@@ -5154,7 +5154,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706115245819</v>
+        <v>1.47706127166748</v>
       </c>
       <c r="H165" t="n">
         <v>4400</v>
@@ -52575,6 +52575,35 @@
         <v>38500</v>
       </c>
       <c r="I1800" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1801" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1801" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D1801" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E1801" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F1801" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="G1801" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="H1801" t="n">
+        <v>167750</v>
+      </c>
+      <c r="I1801" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H2" t="n">
         <v>789800</v>
@@ -514,7 +514,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100511550903</v>
+        <v>2.06100487709045</v>
       </c>
       <c r="H5" t="n">
         <v>390500</v>
@@ -543,7 +543,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H6" t="n">
         <v>204600</v>
@@ -572,7 +572,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H7" t="n">
         <v>304700</v>
@@ -601,7 +601,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H8" t="n">
         <v>64900</v>
@@ -630,7 +630,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H9" t="n">
         <v>221100</v>
@@ -688,7 +688,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H11" t="n">
         <v>48400</v>
@@ -717,7 +717,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H12" t="n">
         <v>114400</v>
@@ -833,7 +833,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081661224365</v>
+        <v>2.22081685066223</v>
       </c>
       <c r="H16" t="n">
         <v>167200</v>
@@ -1152,7 +1152,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534410476685</v>
+        <v>2.05534434318542</v>
       </c>
       <c r="H27" t="n">
         <v>31900</v>
@@ -1181,7 +1181,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H28" t="n">
         <v>36300</v>
@@ -1268,7 +1268,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H31" t="n">
         <v>28600</v>
@@ -1384,7 +1384,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H35" t="n">
         <v>13200</v>
@@ -1529,7 +1529,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276272773743</v>
+        <v>2.07276248931885</v>
       </c>
       <c r="H40" t="n">
         <v>35200</v>
@@ -1558,7 +1558,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663515090942</v>
+        <v>2.04663491249084</v>
       </c>
       <c r="H41" t="n">
         <v>5500</v>
@@ -1587,7 +1587,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H42" t="n">
         <v>14300</v>
@@ -1616,7 +1616,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438107013702</v>
+        <v>1.99438095092773</v>
       </c>
       <c r="H43" t="n">
         <v>44000</v>
@@ -1645,7 +1645,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H44" t="n">
         <v>13200</v>
@@ -1674,7 +1674,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H45" t="n">
         <v>22000</v>
@@ -1703,7 +1703,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179909706116</v>
+        <v>2.01179933547974</v>
       </c>
       <c r="H46" t="n">
         <v>9900</v>
@@ -1732,7 +1732,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H47" t="n">
         <v>202400</v>
@@ -1761,7 +1761,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H48" t="n">
         <v>19800</v>
@@ -1848,7 +1848,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212591648102</v>
+        <v>1.94212603569031</v>
       </c>
       <c r="H51" t="n">
         <v>24200</v>
@@ -1877,7 +1877,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H52" t="n">
         <v>77000</v>
@@ -1935,7 +1935,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729010105133</v>
+        <v>1.90729022026062</v>
       </c>
       <c r="H54" t="n">
         <v>37400</v>
@@ -1993,7 +1993,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858102798462</v>
+        <v>1.89858090877533</v>
       </c>
       <c r="H56" t="n">
         <v>31900</v>
@@ -2022,7 +2022,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H57" t="n">
         <v>2200</v>
@@ -2080,7 +2080,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H59" t="n">
         <v>48400</v>
@@ -2167,7 +2167,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954430103302</v>
+        <v>1.95954442024231</v>
       </c>
       <c r="H62" t="n">
         <v>18700</v>
@@ -2254,7 +2254,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954430103302</v>
+        <v>1.95954442024231</v>
       </c>
       <c r="H65" t="n">
         <v>20900</v>
@@ -2486,7 +2486,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H73" t="n">
         <v>14300</v>
@@ -2544,7 +2544,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H75" t="n">
         <v>8800</v>
@@ -2573,7 +2573,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.85503506660461</v>
+        <v>1.8550351858139</v>
       </c>
       <c r="H76" t="n">
         <v>6600</v>
@@ -2602,7 +2602,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H77" t="n">
         <v>4400</v>
@@ -2718,7 +2718,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.8463259935379</v>
+        <v>1.84632587432861</v>
       </c>
       <c r="H81" t="n">
         <v>5500</v>
@@ -2805,7 +2805,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.79407203197479</v>
+        <v>1.7940719127655</v>
       </c>
       <c r="H84" t="n">
         <v>7700</v>
@@ -2950,7 +2950,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H89" t="n">
         <v>77000</v>
@@ -3037,7 +3037,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H92" t="n">
         <v>78100</v>
@@ -3066,7 +3066,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696256637573</v>
+        <v>1.97696268558502</v>
       </c>
       <c r="H93" t="n">
         <v>28600</v>
@@ -3095,7 +3095,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309014320374</v>
+        <v>2.00309038162231</v>
       </c>
       <c r="H94" t="n">
         <v>63800</v>
@@ -3124,7 +3124,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534410476685</v>
+        <v>2.05534434318542</v>
       </c>
       <c r="H95" t="n">
         <v>22000</v>
@@ -3182,7 +3182,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792595863342</v>
+        <v>2.03792572021484</v>
       </c>
       <c r="H97" t="n">
         <v>79200</v>
@@ -3211,7 +3211,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083498954773</v>
+        <v>1.95083510875702</v>
       </c>
       <c r="H98" t="n">
         <v>44000</v>
@@ -3240,7 +3240,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729010105133</v>
+        <v>1.90729022026062</v>
       </c>
       <c r="H99" t="n">
         <v>19800</v>
@@ -3298,7 +3298,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987171649933</v>
+        <v>1.88987183570862</v>
       </c>
       <c r="H101" t="n">
         <v>9900</v>
@@ -3617,7 +3617,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896297931671</v>
+        <v>1.01896286010742</v>
       </c>
       <c r="H112" t="n">
         <v>29700</v>
@@ -3762,7 +3762,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744671821594</v>
+        <v>0.905744612216949</v>
       </c>
       <c r="H117" t="n">
         <v>7700</v>
@@ -3878,7 +3878,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927201747894</v>
+        <v>1.21927213668823</v>
       </c>
       <c r="H121" t="n">
         <v>14300</v>
@@ -3907,7 +3907,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927201747894</v>
+        <v>1.21927213668823</v>
       </c>
       <c r="H122" t="n">
         <v>45100</v>
@@ -3936,7 +3936,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894460201263</v>
+        <v>1.28894448280334</v>
       </c>
       <c r="H123" t="n">
         <v>45100</v>
@@ -3965,7 +3965,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894460201263</v>
+        <v>1.28894448280334</v>
       </c>
       <c r="H124" t="n">
         <v>34100</v>
@@ -4139,7 +4139,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990775585175</v>
+        <v>1.34990787506104</v>
       </c>
       <c r="H130" t="n">
         <v>6600</v>
@@ -4168,7 +4168,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H131" t="n">
         <v>15400</v>
@@ -4197,7 +4197,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H132" t="n">
         <v>60500</v>
@@ -4226,7 +4226,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783964633942</v>
+        <v>1.41783952713013</v>
       </c>
       <c r="H133" t="n">
         <v>38500</v>
@@ -4284,7 +4284,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474440574646</v>
+        <v>1.38474452495575</v>
       </c>
       <c r="H135" t="n">
         <v>6600</v>
@@ -4342,7 +4342,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501046657562</v>
+        <v>1.27501034736633</v>
       </c>
       <c r="H137" t="n">
         <v>9900</v>
@@ -4400,7 +4400,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378137111664</v>
+        <v>1.32378125190735</v>
       </c>
       <c r="H139" t="n">
         <v>17600</v>
@@ -4429,7 +4429,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409040927887</v>
+        <v>1.52409029006958</v>
       </c>
       <c r="H140" t="n">
         <v>67100</v>
@@ -4487,7 +4487,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441687107086</v>
+        <v>1.45441699028015</v>
       </c>
       <c r="H142" t="n">
         <v>73700</v>
@@ -4574,7 +4574,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113708972931</v>
+        <v>1.30113697052002</v>
       </c>
       <c r="H145" t="n">
         <v>9900</v>
@@ -4632,7 +4632,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119963645935</v>
+        <v>1.34119951725006</v>
       </c>
       <c r="H147" t="n">
         <v>14300</v>
@@ -4748,7 +4748,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H151" t="n">
         <v>8800</v>
@@ -4777,7 +4777,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042126178741</v>
+        <v>1.40042114257812</v>
       </c>
       <c r="H152" t="n">
         <v>7700</v>
@@ -4806,7 +4806,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H153" t="n">
         <v>3300</v>
@@ -4835,7 +4835,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345371723175</v>
+        <v>1.39345359802246</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054444789886</v>
+        <v>1.48054456710815</v>
       </c>
       <c r="H163" t="n">
         <v>9900</v>
@@ -5154,7 +5154,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706127166748</v>
+        <v>1.47706115245819</v>
       </c>
       <c r="H165" t="n">
         <v>4400</v>
@@ -52604,6 +52604,35 @@
         <v>167750</v>
       </c>
       <c r="I1801" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1802" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1802" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="D1802" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E1802" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F1802" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="G1802" t="n">
+        <v>1.45000004768372</v>
+      </c>
+      <c r="H1802" t="n">
+        <v>20900</v>
+      </c>
+      <c r="I1802" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBS.MI.xlsx
+++ b/data/WBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H2" t="n">
         <v>789800</v>
@@ -514,7 +514,7 @@
         <v>2.15136289596558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06100487709045</v>
+        <v>2.06100511550903</v>
       </c>
       <c r="H5" t="n">
         <v>390500</v>
@@ -543,7 +543,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H6" t="n">
         <v>204600</v>
@@ -572,7 +572,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H7" t="n">
         <v>304700</v>
@@ -601,7 +601,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H8" t="n">
         <v>64900</v>
@@ -630,7 +630,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H9" t="n">
         <v>221100</v>
@@ -688,7 +688,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H11" t="n">
         <v>48400</v>
@@ -717,7 +717,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H12" t="n">
         <v>114400</v>
@@ -833,7 +833,7 @@
         <v>2.31818103790283</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22081685066223</v>
+        <v>2.22081661224365</v>
       </c>
       <c r="H16" t="n">
         <v>167200</v>
@@ -1152,7 +1152,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H27" t="n">
         <v>31900</v>
@@ -1181,7 +1181,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H28" t="n">
         <v>36300</v>
@@ -1268,7 +1268,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G31" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H31" t="n">
         <v>28600</v>
@@ -1384,7 +1384,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H35" t="n">
         <v>13200</v>
@@ -1529,7 +1529,7 @@
         <v>2.16363596916199</v>
       </c>
       <c r="G40" t="n">
-        <v>2.07276248931885</v>
+        <v>2.07276272773743</v>
       </c>
       <c r="H40" t="n">
         <v>35200</v>
@@ -1558,7 +1558,7 @@
         <v>2.13636302947998</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04663491249084</v>
+        <v>2.04663515090942</v>
       </c>
       <c r="H41" t="n">
         <v>5500</v>
@@ -1587,7 +1587,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H42" t="n">
         <v>14300</v>
@@ -1616,7 +1616,7 @@
         <v>2.08181810379028</v>
       </c>
       <c r="G43" t="n">
-        <v>1.99438095092773</v>
+        <v>1.99438107013702</v>
       </c>
       <c r="H43" t="n">
         <v>44000</v>
@@ -1645,7 +1645,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H44" t="n">
         <v>13200</v>
@@ -1674,7 +1674,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H45" t="n">
         <v>22000</v>
@@ -1703,7 +1703,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01179933547974</v>
+        <v>2.01179909706116</v>
       </c>
       <c r="H46" t="n">
         <v>9900</v>
@@ -1732,7 +1732,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G47" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H47" t="n">
         <v>202400</v>
@@ -1761,7 +1761,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H48" t="n">
         <v>19800</v>
@@ -1848,7 +1848,7 @@
         <v>2.02727198600769</v>
       </c>
       <c r="G51" t="n">
-        <v>1.94212603569031</v>
+        <v>1.94212591648102</v>
       </c>
       <c r="H51" t="n">
         <v>24200</v>
@@ -1877,7 +1877,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G52" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H52" t="n">
         <v>77000</v>
@@ -1935,7 +1935,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G54" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H54" t="n">
         <v>37400</v>
@@ -1993,7 +1993,7 @@
         <v>1.98181796073914</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89858090877533</v>
+        <v>1.89858102798462</v>
       </c>
       <c r="H56" t="n">
         <v>31900</v>
@@ -2022,7 +2022,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G57" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H57" t="n">
         <v>2200</v>
@@ -2080,7 +2080,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H59" t="n">
         <v>48400</v>
@@ -2167,7 +2167,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G62" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H62" t="n">
         <v>18700</v>
@@ -2254,7 +2254,7 @@
         <v>2.04545402526855</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95954442024231</v>
+        <v>1.95954430103302</v>
       </c>
       <c r="H65" t="n">
         <v>20900</v>
@@ -2486,7 +2486,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G73" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H73" t="n">
         <v>14300</v>
@@ -2544,7 +2544,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H75" t="n">
         <v>8800</v>
@@ -2573,7 +2573,7 @@
         <v>1.93636298179626</v>
       </c>
       <c r="G76" t="n">
-        <v>1.8550351858139</v>
+        <v>1.85503506660461</v>
       </c>
       <c r="H76" t="n">
         <v>6600</v>
@@ -2602,7 +2602,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G77" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H77" t="n">
         <v>4400</v>
@@ -2718,7 +2718,7 @@
         <v>1.92727196216583</v>
       </c>
       <c r="G81" t="n">
-        <v>1.84632587432861</v>
+        <v>1.8463259935379</v>
       </c>
       <c r="H81" t="n">
         <v>5500</v>
@@ -2805,7 +2805,7 @@
         <v>1.87272703647614</v>
       </c>
       <c r="G84" t="n">
-        <v>1.7940719127655</v>
+        <v>1.79407203197479</v>
       </c>
       <c r="H84" t="n">
         <v>7700</v>
@@ -2950,7 +2950,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H89" t="n">
         <v>77000</v>
@@ -3037,7 +3037,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H92" t="n">
         <v>78100</v>
@@ -3066,7 +3066,7 @@
         <v>2.06363606452942</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97696268558502</v>
+        <v>1.97696256637573</v>
       </c>
       <c r="H93" t="n">
         <v>28600</v>
@@ -3095,7 +3095,7 @@
         <v>2.09090900421143</v>
       </c>
       <c r="G94" t="n">
-        <v>2.00309038162231</v>
+        <v>2.00309014320374</v>
       </c>
       <c r="H94" t="n">
         <v>63800</v>
@@ -3124,7 +3124,7 @@
         <v>2.14545392990112</v>
       </c>
       <c r="G95" t="n">
-        <v>2.05534434318542</v>
+        <v>2.05534410476685</v>
       </c>
       <c r="H95" t="n">
         <v>22000</v>
@@ -3182,7 +3182,7 @@
         <v>2.12727189064026</v>
       </c>
       <c r="G97" t="n">
-        <v>2.03792572021484</v>
+        <v>2.03792595863342</v>
       </c>
       <c r="H97" t="n">
         <v>79200</v>
@@ -3211,7 +3211,7 @@
         <v>2.03636288642883</v>
       </c>
       <c r="G98" t="n">
-        <v>1.95083510875702</v>
+        <v>1.95083498954773</v>
       </c>
       <c r="H98" t="n">
         <v>44000</v>
@@ -3240,7 +3240,7 @@
         <v>1.99090898036957</v>
       </c>
       <c r="G99" t="n">
-        <v>1.90729022026062</v>
+        <v>1.90729010105133</v>
       </c>
       <c r="H99" t="n">
         <v>19800</v>
@@ -3298,7 +3298,7 @@
         <v>1.9727269411087</v>
       </c>
       <c r="G101" t="n">
-        <v>1.88987183570862</v>
+        <v>1.88987171649933</v>
       </c>
       <c r="H101" t="n">
         <v>9900</v>
@@ -3617,7 +3617,7 @@
         <v>1.06363594532013</v>
       </c>
       <c r="G112" t="n">
-        <v>1.01896286010742</v>
+        <v>1.01896297931671</v>
       </c>
       <c r="H112" t="n">
         <v>29700</v>
@@ -3762,7 +3762,7 @@
         <v>0.945454001426697</v>
       </c>
       <c r="G117" t="n">
-        <v>0.905744612216949</v>
+        <v>0.905744671821594</v>
       </c>
       <c r="H117" t="n">
         <v>7700</v>
@@ -3878,7 +3878,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G121" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H121" t="n">
         <v>14300</v>
@@ -3907,7 +3907,7 @@
         <v>1.27272701263428</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21927213668823</v>
+        <v>1.21927201747894</v>
       </c>
       <c r="H122" t="n">
         <v>45100</v>
@@ -3936,7 +3936,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G123" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H123" t="n">
         <v>45100</v>
@@ -3965,7 +3965,7 @@
         <v>1.34545397758484</v>
       </c>
       <c r="G124" t="n">
-        <v>1.28894448280334</v>
+        <v>1.28894460201263</v>
       </c>
       <c r="H124" t="n">
         <v>34100</v>
@@ -4139,7 +4139,7 @@
         <v>1.40909004211426</v>
       </c>
       <c r="G130" t="n">
-        <v>1.34990787506104</v>
+        <v>1.34990775585175</v>
       </c>
       <c r="H130" t="n">
         <v>6600</v>
@@ -4168,7 +4168,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H131" t="n">
         <v>15400</v>
@@ -4197,7 +4197,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G132" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H132" t="n">
         <v>60500</v>
@@ -4226,7 +4226,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>1.41783952713013</v>
+        <v>1.41783964633942</v>
       </c>
       <c r="H133" t="n">
         <v>38500</v>
@@ -4284,7 +4284,7 @@
         <v>1.4454540014267</v>
       </c>
       <c r="G135" t="n">
-        <v>1.38474452495575</v>
+        <v>1.38474440574646</v>
       </c>
       <c r="H135" t="n">
         <v>6600</v>
@@ -4342,7 +4342,7 @@
         <v>1.33090901374817</v>
       </c>
       <c r="G137" t="n">
-        <v>1.27501034736633</v>
+        <v>1.27501046657562</v>
       </c>
       <c r="H137" t="n">
         <v>9900</v>
@@ -4400,7 +4400,7 @@
         <v>1.38181805610657</v>
       </c>
       <c r="G139" t="n">
-        <v>1.32378125190735</v>
+        <v>1.32378137111664</v>
       </c>
       <c r="H139" t="n">
         <v>17600</v>
@@ -4429,7 +4429,7 @@
         <v>1.59090900421143</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52409029006958</v>
+        <v>1.52409040927887</v>
       </c>
       <c r="H140" t="n">
         <v>67100</v>
@@ -4487,7 +4487,7 @@
         <v>1.51818096637726</v>
       </c>
       <c r="G142" t="n">
-        <v>1.45441699028015</v>
+        <v>1.45441687107086</v>
       </c>
       <c r="H142" t="n">
         <v>73700</v>
@@ -4574,7 +4574,7 @@
         <v>1.35818099975586</v>
       </c>
       <c r="G145" t="n">
-        <v>1.30113697052002</v>
+        <v>1.30113708972931</v>
       </c>
       <c r="H145" t="n">
         <v>9900</v>
@@ -4632,7 +4632,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G147" t="n">
-        <v>1.34119951725006</v>
+        <v>1.34119963645935</v>
       </c>
       <c r="H147" t="n">
         <v>14300</v>
@@ -4748,7 +4748,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H151" t="n">
         <v>8800</v>
@@ -4777,7 +4777,7 @@
         <v>1.46181797981262</v>
       </c>
       <c r="G152" t="n">
-        <v>1.40042114257812</v>
+        <v>1.40042126178741</v>
       </c>
       <c r="H152" t="n">
         <v>7700</v>
@@ -4806,7 +4806,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H153" t="n">
         <v>3300</v>
@@ -4835,7 +4835,7 @@
         <v>1.45454502105713</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39345359802246</v>
+        <v>1.39345371723175</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1.54545402526855</v>
       </c>
       <c r="G163" t="n">
-        <v>1.48054456710815</v>
+        <v>1.48054444789886</v>
       </c>
       <c r="H163" t="n">
         <v>9900</v>
@@ -5154,7 +5154,7 @@
         <v>1.54181802272797</v>
       </c>
       <c r="G165" t="n">
-        <v>1.47706115245819</v>
+        <v>1.47706127166748</v>
       </c>
       <c r="H165" t="n">
         <v>4400</v>
@@ -52633,6 +52633,35 @@
         <v>20900</v>
       </c>
       <c r="I1802" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1803" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1803" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="D1803" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="E1803" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F1803" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G1803" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="H1803" t="n">
+        <v>12650</v>
+      </c>
+      <c r="I1803" t="s">
         <v>9</v>
       </c>
     </row>
